--- a/data/trans_dic/IP31KM15_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,02; 79,8</t>
+          <t>41,33; 65,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,95; 60,92</t>
+          <t>61,58; 80,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,45; 67,85</t>
+          <t>55,83; 71,08</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,37; 69,34</t>
+          <t>51,54; 64,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,75; 64,32</t>
+          <t>56,95; 69,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,33; 65,25</t>
+          <t>55,88; 64,86</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,13; 63,42</t>
+          <t>50,13; 62,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,48; 62,94</t>
+          <t>51,98; 64,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,72; 60,97</t>
+          <t>52,96; 61,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 54,68</t>
+          <t>47,65; 60,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,69; 58,97</t>
+          <t>47,69; 58,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,32; 54,72</t>
+          <t>48,83; 57,61</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,69; 59,45</t>
+          <t>51,94; 59,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,79; 57,96</t>
+          <t>54,64; 61,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,2; 57,72</t>
+          <t>54,21; 59,51</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>50658</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27908; 37104</t>
+          <t>15472; 24381</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17186; 27587</t>
+          <t>26281; 34548</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47220; 62268</t>
+          <t>44725; 56950</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>101464</t>
+          <t>90677</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>104957</t>
+          <t>92127</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206422</t>
+          <t>182804</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91384; 110466</t>
+          <t>80941; 100981</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94168; 117031</t>
+          <t>82873; 100701</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>192240; 222683</t>
+          <t>169061; 196227</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>112769</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>120294</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>218024</t>
+          <t>214944</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85033; 109754</t>
+          <t>100330; 125536</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107262; 133750</t>
+          <t>90801; 112942</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>199397; 235077</t>
+          <t>198503; 231651</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>129800</t>
+          <t>156800</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>157967</t>
+          <t>135349</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287767</t>
+          <t>292148</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93856; 149982</t>
+          <t>139237; 176090</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136312; 179851</t>
+          <t>121782; 150245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>245169; 316994</t>
+          <t>267361; 315442</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>535</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>361860</t>
+          <t>380108</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>360446</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>740553</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>311478; 388284</t>
+          <t>356711; 407480</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>378260; 431631</t>
+          <t>337793; 380812</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>715739; 806798</t>
+          <t>707394; 776670</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM15_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM15_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman 2 yogures y/o 40 g de queso cada día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>53,06%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>72,16%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>41,33; 65,13</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>61,58; 80,94</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55,83; 71,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>57,74%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>63,31%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>51,54; 64,3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>56,95; 69,2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>55,88; 64,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>56,35%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>58,5%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>50,13; 62,73</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>51,98; 64,66</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>52,96; 61,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>53,66%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53,01%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>47,65; 60,26</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>47,69; 58,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48,83; 57,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>55,34%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58,31%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>56,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>51,94; 59,33</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54,64; 61,6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>54,21; 59,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5305553242487545</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7215563947591361</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6323087801975817</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>19861</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30797</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50658</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.413298191058772</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6157574092565994</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5582515877266663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>15472; 24381</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26281; 34548</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>44725; 56950</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6512952294459774</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8094383230472272</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7108474026751201</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5774072388062084</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6330942436887966</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6041901934403923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>90677</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92127</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>182804</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5154068414744465</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5695023554542445</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5587673102197208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>80941; 100981</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>82873; 100701</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>169061; 196227</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6430196943671628</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.692015118220956</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6485570029446216</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5634904199609503</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5849510469334629</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5734920089003981</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>112769</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>102175</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>214944</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5013364642936655</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.519839556097959</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5296261771090993</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>100330; 125536</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>90801; 112942</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>198503; 231651</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6272831475295966</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6465960207854254</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6180680027785959</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5365799561146415</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5300779473406974</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5335479404280589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>156800</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>135349</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>292148</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.476479871106931</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4769442959359563</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4882787010559925</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>139237; 176090</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>121782; 150245</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>267361; 315442</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6025912132492124</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.588418490833465</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5760880401805715</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5534278688418931</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5830503165329192</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5674603474507062</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>380108</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>360446</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5193635760153495</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5464069230718962</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5420516225005888</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>356711; 407480</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>337793; 380812</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>707394; 776670</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5932814819740828</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6159926674253522</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5951354530144641</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman 2 yogures y/o 40 g de queso cada día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>19861</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>30797</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>50658</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>15472</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>26281</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>44725</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24381</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>34548</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>56950</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>90677</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>92127</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>182804</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>80941</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>82873</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>169061</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>100981</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>100701</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>196227</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>112769</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>102175</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>214944</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>100330</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>90801</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>198503</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>125536</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>112942</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>231651</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>156800</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>135349</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>292148</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>139237</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>121782</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>267361</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>176090</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>150245</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>315442</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>505</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>535</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>380108</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>360446</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>740553</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>356711</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>337793</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>707394</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>407480</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>380812</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>776670</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>